--- a/data/2026_VBS_Boat_Inventory_Master.xlsx
+++ b/data/2026_VBS_Boat_Inventory_Master.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="866">
   <si>
     <t>YEAR</t>
   </si>
@@ -110,7 +110,7 @@
     <t>clarks-landing-yacht-sales-and-marina__cutwater-boats__288__2026</t>
   </si>
   <si>
-    <t>248</t>
+    <t>C-248 C</t>
   </si>
   <si>
     <t>https://www.clarkslanding.com/inventory/2026-Cutwater-c-248-coupe-cw073</t>
@@ -788,7 +788,7 @@
     <t>dandr-boat-world__world-cat-boats__230-dual-console__2026</t>
   </si>
   <si>
-    <t>265 Dual Console</t>
+    <t>265DC-X</t>
   </si>
   <si>
     <t>https://www.dnrboatworld.com/NEW-Inventory-2026-World-Cat-Boat-265-DC-X-D-R-Boat-World-17799165?ref=list</t>
@@ -1325,7 +1325,7 @@
     <t>new-jersey-outboards__parker-boats__227-explorer__2026</t>
   </si>
   <si>
-    <t>230 Coastal Edition</t>
+    <t>230 Coastal Elite</t>
   </si>
   <si>
     <t>PA2605</t>
@@ -1337,7 +1337,7 @@
     <t>new-jersey-outboards__parker-boats__230-coastal-edition__2026</t>
   </si>
   <si>
-    <t>2100 SE CC</t>
+    <t>2100 Special Edition</t>
   </si>
   <si>
     <t>PA2517</t>
@@ -1349,7 +1349,7 @@
     <t>new-jersey-outboards__parker-boats__2100-se-cc__2025</t>
   </si>
   <si>
-    <t>180 Coastal Edition</t>
+    <t>180 Coastal</t>
   </si>
   <si>
     <t>https://www.njoutboards.com/New-Inventory-2026-Parker-Boat-180-Coastal-New-Jersey-Outboards-18205049</t>
@@ -2273,7 +2273,7 @@
     <t>stone-harbor-marina__sea-pro__292-dlx__2026</t>
   </si>
   <si>
-    <t>262 DLX</t>
+    <t>262 Offshore DLX</t>
   </si>
   <si>
     <t>N83653</t>
@@ -2631,6 +2631,9 @@
   </si>
   <si>
     <t>Aug 30, 2026 - Dropped 2 Comstock rows on dealer-inventory evidence. (1) Grady-White 321 Coastal Explorer: all 20 Grady-Whites in Comstock's own live inventory were enumerated and none is a Coastal Explorer of any size; their Coastal Explorer model page tops out at a stale 2023 251 CE; and John Eskow's complete at-show list omits it. (2) Grady-White Canyon 336: Comstock's unfiltered inventory shows no 336, their only 336 page is marked 'Availability: Brochure', and Boat Trader shows no Comstock 336 in NJ; this workbook's own earlier note already said Comstock has no new Canyon 266 or 336 in stock. Both models remain listed under MarineMax, which holds real units, so neither boat leaves the show - only Comstock's claim to them. SHARED WITH was recomputed after the deletion: these two models are no longer shared, so shared rows fall 26 -&gt; 22. Boat rows 205 -&gt; 203. NOTE STILL OPEN: Comstock Grady-White Canyon 266 was ruled ASK, not DROP (the 266 is an all-new MY2027 debut, so absence from stock is not proof), and it is the sole dealer credited for that boat on the live site - confirm with John Eskow before the show.</t>
+  </si>
+  <si>
+    <t>Aug 31, 2026 - Corrected 6 model names to match the manufacturer's own live model page: Parker 180 Coastal Edition -&gt; 180 Coastal (Coastal Elite is an upgrade package, not a model); Parker 230 Coastal Edition -&gt; 230 Coastal Elite; Parker 2100 SE CC -&gt; 2100 Special Edition (line discontinued, Parker's page 404s, name taken from their own spec sheet); Cutwater 248 -&gt; C-248 C; World Cat 265 Dual Console -&gt; 265DC-X; Sea Pro 262 DLX -&gt; 262 Offshore DLX (Sea Pro sells the 262 Offshore in Sport and DLX trims, there is no standalone 262 DLX). Model YEARS were deliberately left alone: a manufacturer promoting the current year on its site says nothing about which year hull a dealer has on the floor. FOUR NAMES STILL NEED A DEALER TO SETTLE, left unchanged on purpose: Cutwater 288 (Cutwater sells a C-288 C Coupe and a C-288 CB Command Bridge and the listing does not say which is on display; the site copy currently describes the Coupe); Sea Hunt Ultra 275CB (seahuntboats.com now 301-redirects 275CB to 275SL and no CB trim remains in the Ultra line, but Sea Hunt has published no statement, so this may be a mid-year rename); Robalo 237 Dual Console (real as a 2027 build but Robalo has published no 2027 model pages, and one dealer build sheet described it as a center console); StarCraft SVX 230 DC OB is CORRECT and must not be changed to 231 DC OB, which is a CMS slug error on Starcraft's own site, and a separate 231 OB exists in the lineup. The website pins these boats to their original URLs, so the rename is display-only: no page moved, no photos were lost and no description was orphaned.</t>
   </si>
 </sst>
 </file>
@@ -7937,7 +7940,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="130" customWidth="1"/>
@@ -8179,6 +8182,11 @@
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>864</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>865</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026_VBS_Boat_Inventory_Master.xlsx
+++ b/data/2026_VBS_Boat_Inventory_Master.xlsx
@@ -21,7 +21,7 @@
     <sheet sheetId="12" name="TBD - Unknown 2" state="visible" r:id="rId15"/>
     <sheet sheetId="13" name="TBD - Brig Jeanneau" state="visible" r:id="rId16"/>
     <sheet sheetId="14" name="Sandy Hook" state="visible" r:id="rId17"/>
-    <sheet sheetId="15" name="TBD - Cape Horn NorthCoast" state="visible" r:id="rId18"/>
+    <sheet sheetId="15" name="Seaport Inlet" state="visible" r:id="rId18"/>
     <sheet sheetId="16" name="Schrader" state="visible" r:id="rId19"/>
     <sheet sheetId="17" name="Sheltered Cove" state="visible" r:id="rId20"/>
     <sheet sheetId="18" name="South Jersey" state="visible" r:id="rId21"/>
@@ -30,13 +30,14 @@
     <sheet sheetId="21" name="TBD - Contender Monterey" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Dealer Contacts" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="Notes" state="visible" r:id="rId26"/>
+    <sheet sheetId="24" name="Irwin" state="visible" r:id="rId27"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="913">
   <si>
     <t>YEAR</t>
   </si>
@@ -1724,6 +1725,69 @@
     <t>tbd-cape-horn-northcoast__northcoast-boats</t>
   </si>
   <si>
+    <t>415 HT</t>
+  </si>
+  <si>
+    <t>https://www.seaportinletmarina.com/new-boat-showrooms/northcoast/2026-northcoast-415-ht-10003207/</t>
+  </si>
+  <si>
+    <t>https://www.northcoastboats.com/</t>
+  </si>
+  <si>
+    <t>Seaport Inlet Marina</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__northcoast-boats__415-ht__2026</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__northcoast-boats__315__2026</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__northcoast-boats__285__2026</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__northcoast-boats__255__2026</t>
+  </si>
+  <si>
+    <t>39XS</t>
+  </si>
+  <si>
+    <t>https://www.seaportinletmarina.com/new-boat-showrooms/cape-horn/2027-cape-horn-39xs-10283666/</t>
+  </si>
+  <si>
+    <t>https://www.capehornboats.com/</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__cape-horn-boats__39xs__2027</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__cape-horn-boats__36__2026</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__cape-horn-boats__34__2026</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__cape-horn-boats__31__2026</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__cape-horn-boats__28__2026</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
@@ -2492,6 +2556,33 @@
     <t>PLAN B fallback (decided Aug 30) - replace when the dealer supplies a lead inbox. Not yet supplied - 23-boat list from Giselle's Aug 22 xlsx verified line by line Aug 30 (stock numbers and feature priority added to tab)</t>
   </si>
   <si>
+    <t>Irwin Marine Center</t>
+  </si>
+  <si>
+    <t>Tim Ryan, Regional Manager, Sagamore Blue (tryan@sagamoreblue.com, direct 908-399-5458, office 732-741-0003)</t>
+  </si>
+  <si>
+    <t>Sales@sagamoreblue.com</t>
+  </si>
+  <si>
+    <t>908-399-5458</t>
+  </si>
+  <si>
+    <t>Tim Ryan email, Sep 1 (forwarded by Giselle)</t>
+  </si>
+  <si>
+    <t>Christian Matthews, Sales Manager (moved from Coastal Boat Sales Aug 2026)</t>
+  </si>
+  <si>
+    <t>Christian.seaport@gmail.com</t>
+  </si>
+  <si>
+    <t>732-757-5157</t>
+  </si>
+  <si>
+    <t>Christian Matthews email, Sep 1 (forwarded by Giselle)</t>
+  </si>
+  <si>
     <t>2026 AC In-Water Virtual Boat Show - Boat Inventory Master (built Aug 30, 2026)</t>
   </si>
   <si>
@@ -2634,6 +2725,57 @@
   </si>
   <si>
     <t>Aug 31, 2026 - Corrected 6 model names to match the manufacturer's own live model page: Parker 180 Coastal Edition -&gt; 180 Coastal (Coastal Elite is an upgrade package, not a model); Parker 230 Coastal Edition -&gt; 230 Coastal Elite; Parker 2100 SE CC -&gt; 2100 Special Edition (line discontinued, Parker's page 404s, name taken from their own spec sheet); Cutwater 248 -&gt; C-248 C; World Cat 265 Dual Console -&gt; 265DC-X; Sea Pro 262 DLX -&gt; 262 Offshore DLX (Sea Pro sells the 262 Offshore in Sport and DLX trims, there is no standalone 262 DLX). Model YEARS were deliberately left alone: a manufacturer promoting the current year on its site says nothing about which year hull a dealer has on the floor. FOUR NAMES STILL NEED A DEALER TO SETTLE, left unchanged on purpose: Cutwater 288 (Cutwater sells a C-288 C Coupe and a C-288 CB Command Bridge and the listing does not say which is on display; the site copy currently describes the Coupe); Sea Hunt Ultra 275CB (seahuntboats.com now 301-redirects 275CB to 275SL and no CB trim remains in the Ultra line, but Sea Hunt has published no statement, so this may be a mid-year rename); Robalo 237 Dual Console (real as a 2027 build but Robalo has published no 2027 model pages, and one dealer build sheet described it as a center console); StarCraft SVX 230 DC OB is CORRECT and must not be changed to 231 DC OB, which is a CMS slug error on Starcraft's own site, and a separate 231 OB exists in the lineup. The website pins these boats to their original URLs, so the rename is display-only: no page moved, no photos were lost and no description was orphaned.</t>
+  </si>
+  <si>
+    <t>Sep 1 dealer submissions added: Seaport Inlet Marina claimed the TBD - Cape Horn NorthCoast tab (tab renamed Seaport Inlet) with a 9-boat lineup - NorthCoast 415 HT/315/285/255 and Cape Horn 39XS/36/34/31/28; only the 415 HT and 39XS carry listing links, the other 7 have no link and no model year (importer applies the 2026 default). Irwin Marine Center added as a new tab with 4 models, all link-backed: Southport 30 FE, Sailfish 316 DC / 252 CC / 245 DC. Irwin was sent Giselle's older template which never asked for a complete at-show lineup, so those 4 may be featured models rather than the full display - and a July note records Irwin also carrying Regal, which Tim Ryan did not list. Both dealers supplied a lead inbox and an on-site text number (see Dealer Contacts).</t>
+  </si>
+  <si>
+    <t>Southport Boats</t>
+  </si>
+  <si>
+    <t>30 FE</t>
+  </si>
+  <si>
+    <t>https://www.irwinmarinecenter.com/boats-for-sale/2026-southport-30-fe-red-bank-united-states-9992063/</t>
+  </si>
+  <si>
+    <t>https://www.southportboats.com/</t>
+  </si>
+  <si>
+    <t>irwin-marine-center__southport-boats__30-fe__2026</t>
+  </si>
+  <si>
+    <t>Sailfish Boats</t>
+  </si>
+  <si>
+    <t>316 DC</t>
+  </si>
+  <si>
+    <t>https://www.irwinmarinecenter.com/boats-for-sale/2027-sailfish-316-dc-red-bank-united-states-10240377/</t>
+  </si>
+  <si>
+    <t>https://www.sailfishboats.com/</t>
+  </si>
+  <si>
+    <t>irwin-marine-center__sailfish-boats__316-dc__2027</t>
+  </si>
+  <si>
+    <t>252 CC</t>
+  </si>
+  <si>
+    <t>https://www.irwinmarinecenter.com/boats-for-sale/2026-sailfish-252-cc-red-bank-united-states-10238694/</t>
+  </si>
+  <si>
+    <t>irwin-marine-center__sailfish-boats__252-cc__2026</t>
+  </si>
+  <si>
+    <t>245 DC</t>
+  </si>
+  <si>
+    <t>https://www.irwinmarinecenter.com/boats-for-sale/2027-sailfish-245-dc-red-bank-united-states-10238691/</t>
+  </si>
+  <si>
+    <t>irwin-marine-center__sailfish-boats__245-dc__2027</t>
   </si>
 </sst>
 </file>
@@ -5109,7 +5251,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -5188,6 +5330,267 @@
         <v>17</v>
       </c>
       <c r="I3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4" t="s">
+        <v>560</v>
+      </c>
+      <c r="C4" t="s">
+        <v>562</v>
+      </c>
+      <c r="D4" t="s">
+        <v>563</v>
+      </c>
+      <c r="E4" t="s">
+        <v>564</v>
+      </c>
+      <c r="F4" t="s">
+        <v>565</v>
+      </c>
+      <c r="G4" t="s">
+        <v>566</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>560</v>
+      </c>
+      <c r="C5" t="s">
+        <v>567</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>564</v>
+      </c>
+      <c r="F5" t="s">
+        <v>565</v>
+      </c>
+      <c r="G5" t="s">
+        <v>568</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>560</v>
+      </c>
+      <c r="C6" t="s">
+        <v>569</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>564</v>
+      </c>
+      <c r="F6" t="s">
+        <v>565</v>
+      </c>
+      <c r="G6" t="s">
+        <v>570</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>560</v>
+      </c>
+      <c r="C7" t="s">
+        <v>571</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>564</v>
+      </c>
+      <c r="F7" t="s">
+        <v>565</v>
+      </c>
+      <c r="G7" t="s">
+        <v>572</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2027</v>
+      </c>
+      <c r="B8" t="s">
+        <v>558</v>
+      </c>
+      <c r="C8" t="s">
+        <v>573</v>
+      </c>
+      <c r="D8" t="s">
+        <v>574</v>
+      </c>
+      <c r="E8" t="s">
+        <v>575</v>
+      </c>
+      <c r="F8" t="s">
+        <v>565</v>
+      </c>
+      <c r="G8" t="s">
+        <v>576</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>558</v>
+      </c>
+      <c r="C9" t="s">
+        <v>577</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>575</v>
+      </c>
+      <c r="F9" t="s">
+        <v>565</v>
+      </c>
+      <c r="G9" t="s">
+        <v>578</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>558</v>
+      </c>
+      <c r="C10" t="s">
+        <v>579</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>575</v>
+      </c>
+      <c r="F10" t="s">
+        <v>565</v>
+      </c>
+      <c r="G10" t="s">
+        <v>580</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>558</v>
+      </c>
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>575</v>
+      </c>
+      <c r="F11" t="s">
+        <v>565</v>
+      </c>
+      <c r="G11" t="s">
+        <v>581</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s">
+        <v>575</v>
+      </c>
+      <c r="F12" t="s">
+        <v>565</v>
+      </c>
+      <c r="G12" t="s">
+        <v>582</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" t="s">
         <v>173</v>
       </c>
     </row>
@@ -5247,25 +5650,25 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="G2" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="H2" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -5279,22 +5682,22 @@
         <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="G3" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="H3" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -5308,22 +5711,22 @@
         <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="G4" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="H4" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="I4" t="s">
         <v>17</v>
@@ -5337,22 +5740,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="G5" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="H5" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -5366,22 +5769,22 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="G6" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="H6" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -5393,21 +5796,21 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
       <c r="G7" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="H7" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -5419,19 +5822,19 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="G8" t="s">
         <v>588</v>
       </c>
-      <c r="G8" t="s">
-        <v>567</v>
-      </c>
       <c r="H8" t="s">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
@@ -5512,22 +5915,22 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>591</v>
+        <v>612</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>592</v>
+        <v>613</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>593</v>
+        <v>614</v>
       </c>
       <c r="G2" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="H2" t="s">
-        <v>595</v>
+        <v>616</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -5541,22 +5944,22 @@
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>597</v>
+        <v>618</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>593</v>
+        <v>614</v>
       </c>
       <c r="G3" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="H3" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -5570,22 +5973,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>600</v>
+        <v>621</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
       <c r="G4" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="H4" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
       <c r="I4" t="s">
         <v>17</v>
@@ -5599,22 +6002,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
       <c r="G5" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="H5" t="s">
-        <v>606</v>
+        <v>627</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -5628,22 +6031,22 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
       <c r="G6" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="H6" t="s">
-        <v>609</v>
+        <v>630</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -5657,22 +6060,22 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
       <c r="G7" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="H7" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -5686,22 +6089,22 @@
         <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>614</v>
+        <v>635</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="G8" t="s">
         <v>615</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="G8" t="s">
-        <v>594</v>
-      </c>
       <c r="H8" t="s">
-        <v>617</v>
+        <v>638</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
@@ -5715,22 +6118,22 @@
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
       <c r="G9" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="H9" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="I9" t="s">
         <v>17</v>
@@ -5744,22 +6147,22 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>621</v>
+        <v>642</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
       <c r="G10" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="H10" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -5773,22 +6176,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>624</v>
+        <v>645</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>625</v>
+        <v>646</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
       <c r="G11" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="H11" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -5802,22 +6205,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
       <c r="G12" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="H12" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="I12" t="s">
         <v>17</v>
@@ -5829,7 +6232,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>630</v>
+        <v>651</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -5838,10 +6241,10 @@
         <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="H13" t="s">
-        <v>631</v>
+        <v>652</v>
       </c>
       <c r="I13" t="s">
         <v>17</v>
@@ -5929,22 +6332,22 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>633</v>
+        <v>654</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>634</v>
+        <v>655</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
       <c r="F2" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="G2" t="s">
-        <v>637</v>
+        <v>658</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -5958,22 +6361,22 @@
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>638</v>
+        <v>659</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>639</v>
+        <v>660</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
       <c r="F3" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="G3" t="s">
-        <v>640</v>
+        <v>661</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -5987,22 +6390,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>641</v>
+        <v>662</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>642</v>
+        <v>663</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
       <c r="F4" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="G4" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -6014,22 +6417,22 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>645</v>
+        <v>666</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>646</v>
+        <v>667</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>647</v>
+        <v>668</v>
       </c>
       <c r="F5" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="G5" t="s">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -6043,22 +6446,22 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>649</v>
+        <v>670</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>647</v>
+        <v>668</v>
       </c>
       <c r="F6" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="G6" t="s">
-        <v>651</v>
+        <v>672</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -6072,22 +6475,22 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>653</v>
+        <v>674</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>647</v>
+        <v>668</v>
       </c>
       <c r="F7" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="G7" t="s">
-        <v>654</v>
+        <v>675</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -6099,22 +6502,22 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>655</v>
+        <v>676</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="F8" t="s">
         <v>657</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="F8" t="s">
-        <v>636</v>
-      </c>
       <c r="G8" t="s">
-        <v>659</v>
+        <v>680</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -6126,22 +6529,22 @@
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>660</v>
+        <v>681</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>661</v>
+        <v>682</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>662</v>
+        <v>683</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>663</v>
+        <v>684</v>
       </c>
       <c r="F9" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="G9" t="s">
-        <v>664</v>
+        <v>685</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -6211,7 +6614,7 @@
         <v>361</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -6231,24 +6634,24 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>668</v>
+        <v>689</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>669</v>
+        <v>690</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I2" t="s">
-        <v>671</v>
+        <v>692</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -6262,26 +6665,26 @@
         <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>672</v>
+        <v>693</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="5" t="s">
-        <v>674</v>
+        <v>695</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I3" t="s">
-        <v>675</v>
+        <v>696</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
@@ -6295,24 +6698,24 @@
         <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>676</v>
+        <v>697</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>677</v>
+        <v>698</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5" t="s">
-        <v>678</v>
+        <v>699</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I4" t="s">
-        <v>679</v>
+        <v>700</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -6326,24 +6729,24 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>681</v>
+        <v>702</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>682</v>
+        <v>703</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I5" t="s">
-        <v>683</v>
+        <v>704</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -6357,24 +6760,24 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>685</v>
+        <v>706</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="5" t="s">
-        <v>686</v>
+        <v>707</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I6" t="s">
-        <v>687</v>
+        <v>708</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
@@ -6388,24 +6791,24 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>688</v>
+        <v>709</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>689</v>
+        <v>710</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="s">
-        <v>690</v>
+        <v>711</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I7" t="s">
-        <v>691</v>
+        <v>712</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -6419,24 +6822,24 @@
         <v>39</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>688</v>
+        <v>709</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>692</v>
+        <v>713</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>693</v>
+        <v>714</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
-        <v>694</v>
+        <v>715</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I8" t="s">
-        <v>695</v>
+        <v>716</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -6450,24 +6853,24 @@
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>688</v>
+        <v>709</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>696</v>
+        <v>717</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>693</v>
+        <v>714</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="s">
-        <v>697</v>
+        <v>718</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I9" t="s">
-        <v>698</v>
+        <v>719</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -6481,26 +6884,26 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>688</v>
+        <v>709</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>699</v>
+        <v>720</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>700</v>
+        <v>721</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>701</v>
+        <v>722</v>
       </c>
       <c r="G10" s="5">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I10" t="s">
-        <v>702</v>
+        <v>723</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
@@ -6514,24 +6917,24 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>688</v>
+        <v>709</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>703</v>
+        <v>724</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>704</v>
+        <v>725</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="5" t="s">
-        <v>705</v>
+        <v>726</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I11" t="s">
-        <v>706</v>
+        <v>727</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -6545,24 +6948,24 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>688</v>
+        <v>709</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>707</v>
+        <v>728</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>708</v>
+        <v>729</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="s">
-        <v>709</v>
+        <v>730</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I12" t="s">
-        <v>710</v>
+        <v>731</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
@@ -6576,24 +6979,24 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>712</v>
+        <v>733</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>713</v>
+        <v>734</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>714</v>
+        <v>735</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I13" t="s">
-        <v>715</v>
+        <v>736</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -6607,24 +7010,24 @@
         <v>10</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>716</v>
+        <v>737</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>717</v>
+        <v>738</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I14" t="s">
-        <v>719</v>
+        <v>740</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -6638,24 +7041,24 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>721</v>
+        <v>742</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="5" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I15" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
@@ -6669,24 +7072,24 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="5" t="s">
-        <v>726</v>
+        <v>747</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I16" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
@@ -6700,24 +7103,24 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>728</v>
+        <v>749</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>729</v>
+        <v>750</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="5" t="s">
-        <v>730</v>
+        <v>751</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I17" t="s">
-        <v>731</v>
+        <v>752</v>
       </c>
       <c r="J17" t="s">
         <v>17</v>
@@ -6731,24 +7134,24 @@
         <v>10</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>733</v>
+        <v>754</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="5" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I18" t="s">
-        <v>736</v>
+        <v>757</v>
       </c>
       <c r="J18" t="s">
         <v>17</v>
@@ -6762,24 +7165,24 @@
         <v>10</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>738</v>
+        <v>759</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="s">
-        <v>739</v>
+        <v>760</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I19" t="s">
-        <v>740</v>
+        <v>761</v>
       </c>
       <c r="J19" t="s">
         <v>17</v>
@@ -6793,24 +7196,24 @@
         <v>10</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>741</v>
+        <v>762</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>742</v>
+        <v>763</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
-        <v>743</v>
+        <v>764</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I20" t="s">
-        <v>744</v>
+        <v>765</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
@@ -6824,24 +7227,24 @@
         <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>745</v>
+        <v>766</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
-        <v>746</v>
+        <v>767</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I21" t="s">
-        <v>747</v>
+        <v>768</v>
       </c>
       <c r="J21" t="s">
         <v>17</v>
@@ -6855,26 +7258,26 @@
         <v>39</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>748</v>
+        <v>769</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="s">
-        <v>749</v>
+        <v>770</v>
       </c>
       <c r="G22" s="5">
         <v>4</v>
       </c>
       <c r="H22" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I22" t="s">
-        <v>750</v>
+        <v>771</v>
       </c>
       <c r="J22" t="s">
         <v>17</v>
@@ -6888,24 +7291,24 @@
         <v>10</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>751</v>
+        <v>772</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>752</v>
+        <v>773</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="5" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I23" t="s">
-        <v>754</v>
+        <v>775</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
@@ -6919,26 +7322,26 @@
         <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>755</v>
+        <v>776</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>756</v>
+        <v>777</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="5" t="s">
-        <v>757</v>
+        <v>778</v>
       </c>
       <c r="G24" s="5">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="I24" t="s">
-        <v>758</v>
+        <v>779</v>
       </c>
       <c r="J24" t="s">
         <v>17</v>
@@ -7418,7 +7821,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>759</v>
+        <v>780</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -7427,7 +7830,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -7439,7 +7842,7 @@
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>761</v>
+        <v>782</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -7448,7 +7851,7 @@
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>762</v>
+        <v>783</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -7460,7 +7863,7 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>763</v>
+        <v>784</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -7469,7 +7872,7 @@
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>764</v>
+        <v>785</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -7481,7 +7884,7 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>765</v>
+        <v>786</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -7490,7 +7893,7 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>766</v>
+        <v>787</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -7502,7 +7905,7 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>767</v>
+        <v>788</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -7511,7 +7914,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>768</v>
+        <v>789</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -7573,7 +7976,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>769</v>
+        <v>790</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -7582,7 +7985,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>770</v>
+        <v>791</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -7603,7 +8006,7 @@
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>771</v>
+        <v>792</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -7615,7 +8018,7 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -7624,7 +8027,7 @@
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -7636,7 +8039,7 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>773</v>
+        <v>794</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -7645,7 +8048,7 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>774</v>
+        <v>795</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -7657,7 +8060,7 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>660</v>
+        <v>681</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -7666,7 +8069,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>775</v>
+        <v>796</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -7685,7 +8088,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -7700,16 +8103,16 @@
         <v>6</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>777</v>
+        <v>798</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>778</v>
+        <v>799</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>779</v>
+        <v>800</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7717,16 +8120,16 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>780</v>
+        <v>801</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>782</v>
+        <v>803</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>783</v>
+        <v>804</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7734,16 +8137,16 @@
         <v>52</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>784</v>
+        <v>805</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>785</v>
+        <v>806</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>786</v>
+        <v>807</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -7751,16 +8154,16 @@
         <v>89</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>791</v>
+        <v>812</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -7768,14 +8171,14 @@
         <v>171</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>792</v>
+        <v>813</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>794</v>
+        <v>815</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7783,14 +8186,14 @@
         <v>190</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>795</v>
+        <v>816</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>796</v>
+        <v>817</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7798,14 +8201,14 @@
         <v>259</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>797</v>
+        <v>818</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -7813,16 +8216,16 @@
         <v>91</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>799</v>
+        <v>820</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>800</v>
+        <v>821</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>801</v>
+        <v>822</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>802</v>
+        <v>823</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -7830,14 +8233,14 @@
         <v>369</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>803</v>
+        <v>824</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>804</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -7845,14 +8248,14 @@
         <v>516</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>805</v>
+        <v>826</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>806</v>
+        <v>827</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -7860,74 +8263,108 @@
         <v>545</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>810</v>
+        <v>831</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>811</v>
+        <v>832</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>812</v>
+        <v>833</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>813</v>
+        <v>834</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>814</v>
+        <v>835</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>815</v>
+        <v>836</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>816</v>
+        <v>837</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>796</v>
+        <v>817</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="3" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>817</v>
+        <v>838</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>839</v>
+      </c>
+      <c r="B16" t="s">
+        <v>840</v>
+      </c>
+      <c r="C16" t="s">
+        <v>841</v>
+      </c>
+      <c r="D16" t="s">
+        <v>842</v>
+      </c>
+      <c r="E16" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>565</v>
+      </c>
+      <c r="B17" t="s">
+        <v>844</v>
+      </c>
+      <c r="C17" t="s">
+        <v>845</v>
+      </c>
+      <c r="D17" t="s">
+        <v>846</v>
+      </c>
+      <c r="E17" t="s">
+        <v>847</v>
       </c>
     </row>
   </sheetData>
@@ -7940,7 +8377,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="130" customWidth="1"/>
@@ -7948,92 +8385,92 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>818</v>
+        <v>848</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>819</v>
+        <v>849</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>820</v>
+        <v>850</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>822</v>
+        <v>852</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>823</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>824</v>
+        <v>854</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>825</v>
+        <v>855</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>826</v>
+        <v>856</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>827</v>
+        <v>857</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>828</v>
+        <v>858</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>829</v>
+        <v>859</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>830</v>
+        <v>860</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>831</v>
+        <v>861</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>832</v>
+        <v>862</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>833</v>
+        <v>863</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>834</v>
+        <v>864</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>835</v>
+        <v>865</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -8041,156 +8478,317 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>836</v>
+        <v>866</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>837</v>
+        <v>867</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>838</v>
+        <v>868</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>839</v>
+        <v>869</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>840</v>
+        <v>870</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>841</v>
+        <v>871</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>842</v>
+        <v>872</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>843</v>
+        <v>873</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>844</v>
+        <v>874</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>845</v>
+        <v>875</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>846</v>
+        <v>876</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>847</v>
+        <v>877</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>848</v>
+        <v>878</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>849</v>
+        <v>879</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>850</v>
+        <v>880</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>851</v>
+        <v>881</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>852</v>
+        <v>882</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>853</v>
+        <v>883</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>854</v>
+        <v>884</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>855</v>
+        <v>885</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>856</v>
+        <v>886</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>857</v>
+        <v>887</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>858</v>
+        <v>888</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>859</v>
+        <v>889</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>861</v>
+        <v>891</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>862</v>
+        <v>892</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>863</v>
+        <v>893</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>864</v>
+        <v>894</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>865</v>
+        <v>895</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>896</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="s">
+        <v>897</v>
+      </c>
+      <c r="C2" t="s">
+        <v>898</v>
+      </c>
+      <c r="D2" t="s">
+        <v>899</v>
+      </c>
+      <c r="E2" t="s">
+        <v>900</v>
+      </c>
+      <c r="F2" t="s">
+        <v>839</v>
+      </c>
+      <c r="G2" t="s">
+        <v>901</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2027</v>
+      </c>
+      <c r="B3" t="s">
+        <v>902</v>
+      </c>
+      <c r="C3" t="s">
+        <v>903</v>
+      </c>
+      <c r="D3" t="s">
+        <v>904</v>
+      </c>
+      <c r="E3" t="s">
+        <v>905</v>
+      </c>
+      <c r="F3" t="s">
+        <v>839</v>
+      </c>
+      <c r="G3" t="s">
+        <v>906</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4" t="s">
+        <v>902</v>
+      </c>
+      <c r="C4" t="s">
+        <v>907</v>
+      </c>
+      <c r="D4" t="s">
+        <v>908</v>
+      </c>
+      <c r="E4" t="s">
+        <v>905</v>
+      </c>
+      <c r="F4" t="s">
+        <v>839</v>
+      </c>
+      <c r="G4" t="s">
+        <v>909</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2027</v>
+      </c>
+      <c r="B5" t="s">
+        <v>902</v>
+      </c>
+      <c r="C5" t="s">
+        <v>910</v>
+      </c>
+      <c r="D5" t="s">
+        <v>911</v>
+      </c>
+      <c r="E5" t="s">
+        <v>905</v>
+      </c>
+      <c r="F5" t="s">
+        <v>839</v>
+      </c>
+      <c r="G5" t="s">
+        <v>912</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 

--- a/data/2026_VBS_Boat_Inventory_Master.xlsx
+++ b/data/2026_VBS_Boat_Inventory_Master.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="924">
   <si>
     <t>YEAR</t>
   </si>
@@ -1740,22 +1740,31 @@
     <t>seaport-inlet-marina__northcoast-boats__415-ht__2026</t>
   </si>
   <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>seaport-inlet-marina__northcoast-boats__315__2026</t>
-  </si>
-  <si>
-    <t>285</t>
-  </si>
-  <si>
-    <t>seaport-inlet-marina__northcoast-boats__285__2026</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>seaport-inlet-marina__northcoast-boats__255__2026</t>
+    <t>315 HT</t>
+  </si>
+  <si>
+    <t>https://www.seaportinletmarina.com/new-boat-showrooms/northcoast/2026-northcoast-315-ht-10003199/</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__northcoast-boats__315-ht__2026</t>
+  </si>
+  <si>
+    <t>285 HT</t>
+  </si>
+  <si>
+    <t>https://www.seaportinletmarina.com/new-boat-showrooms/northcoast/2026-northcoast-285-ht-10003200/</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__northcoast-boats__285-ht__2026</t>
+  </si>
+  <si>
+    <t>255 HT</t>
+  </si>
+  <si>
+    <t>https://www.seaportinletmarina.com/new-boat-showrooms/northcoast/2026-northcoast-255-ht-10003202/</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__northcoast-boats__255-ht__2026</t>
   </si>
   <si>
     <t>39XS</t>
@@ -1770,22 +1779,40 @@
     <t>seaport-inlet-marina__cape-horn-boats__39xs__2027</t>
   </si>
   <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>seaport-inlet-marina__cape-horn-boats__36__2026</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>seaport-inlet-marina__cape-horn-boats__34__2026</t>
-  </si>
-  <si>
-    <t>seaport-inlet-marina__cape-horn-boats__31__2026</t>
-  </si>
-  <si>
-    <t>seaport-inlet-marina__cape-horn-boats__28__2026</t>
+    <t>36XS</t>
+  </si>
+  <si>
+    <t>https://www.seaportinletmarina.com/new-boat-showrooms/cape-horn/2027-cape-horn-36xs-10283665/</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__cape-horn-boats__36xs__2027</t>
+  </si>
+  <si>
+    <t>34XS</t>
+  </si>
+  <si>
+    <t>https://www.seaportinletmarina.com/new-boat-showrooms/cape-horn/2027-cape-horn-34xs-10283664/</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__cape-horn-boats__34xs__2027</t>
+  </si>
+  <si>
+    <t>31T</t>
+  </si>
+  <si>
+    <t>https://www.seaportinletmarina.com/new-boat-showrooms/cape-horn/2027-cape-horn-31t-10283655/</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__cape-horn-boats__31t__2027</t>
+  </si>
+  <si>
+    <t>28XS</t>
+  </si>
+  <si>
+    <t>https://www.seaportinletmarina.com/new-boat-showrooms/cape-horn/2027-cape-horn-28xs-10283662/</t>
+  </si>
+  <si>
+    <t>seaport-inlet-marina__cape-horn-boats__28xs__2027</t>
   </si>
   <si>
     <t>2024</t>
@@ -2728,6 +2755,12 @@
   </si>
   <si>
     <t>Sep 1 dealer submissions added: Seaport Inlet Marina claimed the TBD - Cape Horn NorthCoast tab (tab renamed Seaport Inlet) with a 9-boat lineup - NorthCoast 415 HT/315/285/255 and Cape Horn 39XS/36/34/31/28; only the 415 HT and 39XS carry listing links, the other 7 have no link and no model year (importer applies the 2026 default). Irwin Marine Center added as a new tab with 4 models, all link-backed: Southport 30 FE, Sailfish 316 DC / 252 CC / 245 DC. Irwin was sent Giselle's older template which never asked for a complete at-show lineup, so those 4 may be featured models rather than the full display - and a July note records Irwin also carrying Regal, which Tim Ryan did not list. Both dealers supplied a lead inbox and an on-site text number (see Dealer Contacts).</t>
+  </si>
+  <si>
+    <t>Sep 2: Seaport Inlet's own showroom (seaportinletmarina.com/new-boat-showrooms) resolved six of Christian's bare model numbers to exact hulls with listing links: NorthCoast 315/285/255 are all HT, Cape Horn 36 is the 36XS, 31 is the 31T, 28 is the 28XS. Cape Horn 34 is still open because Seaport stocks BOTH a 34T and a 34XS; only Christian can say which is coming to the show, so that row keeps a bare model and no link.</t>
+  </si>
+  <si>
+    <t>Sep 2 ASSUMPTION, confirm with Christian at check-in: Seaport's Cape Horn 34 is published as the 34XS. Seaport stocks both a 34T and a 34XS and Christian supplied only the number. Chosen because his featured Cape Horn is the 39XS and his other resolvable picks run 36XS and 28XS against one 31T. If it is actually the 34T, change this row's model and link to the 34T listing and re-import; nothing else depends on it.</t>
   </si>
   <si>
     <t>Southport Boats</t>
@@ -5363,8 +5396,8 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
+      <c r="A5">
+        <v>2026</v>
       </c>
       <c r="B5" t="s">
         <v>560</v>
@@ -5373,7 +5406,7 @@
         <v>567</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>568</v>
       </c>
       <c r="E5" t="s">
         <v>564</v>
@@ -5382,27 +5415,27 @@
         <v>565</v>
       </c>
       <c r="G5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>17</v>
+      <c r="A6">
+        <v>2026</v>
       </c>
       <c r="B6" t="s">
         <v>560</v>
       </c>
       <c r="C6" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>571</v>
       </c>
       <c r="E6" t="s">
         <v>564</v>
@@ -5411,27 +5444,27 @@
         <v>565</v>
       </c>
       <c r="G6" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
+      <c r="A7">
+        <v>2026</v>
       </c>
       <c r="B7" t="s">
         <v>560</v>
       </c>
       <c r="C7" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>574</v>
       </c>
       <c r="E7" t="s">
         <v>564</v>
@@ -5440,13 +5473,13 @@
         <v>565</v>
       </c>
       <c r="G7" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -5457,19 +5490,19 @@
         <v>558</v>
       </c>
       <c r="C8" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D8" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E8" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F8" t="s">
         <v>565</v>
       </c>
       <c r="G8" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -5479,119 +5512,119 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>17</v>
+      <c r="A9">
+        <v>2027</v>
       </c>
       <c r="B9" t="s">
         <v>558</v>
       </c>
       <c r="C9" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>581</v>
       </c>
       <c r="E9" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F9" t="s">
         <v>565</v>
       </c>
       <c r="G9" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>17</v>
+      <c r="A10">
+        <v>2027</v>
       </c>
       <c r="B10" t="s">
         <v>558</v>
       </c>
       <c r="C10" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>584</v>
       </c>
       <c r="E10" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F10" t="s">
         <v>565</v>
       </c>
       <c r="G10" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>17</v>
+      <c r="A11">
+        <v>2027</v>
       </c>
       <c r="B11" t="s">
         <v>558</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>586</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>587</v>
       </c>
       <c r="E11" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F11" t="s">
         <v>565</v>
       </c>
       <c r="G11" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>17</v>
+      <c r="A12">
+        <v>2027</v>
       </c>
       <c r="B12" t="s">
         <v>558</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>589</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>590</v>
       </c>
       <c r="E12" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F12" t="s">
         <v>565</v>
       </c>
       <c r="G12" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -5650,25 +5683,25 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="G2" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="H2" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -5682,22 +5715,22 @@
         <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="G3" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="H3" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -5711,22 +5744,22 @@
         <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="G4" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="H4" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="I4" t="s">
         <v>17</v>
@@ -5740,22 +5773,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="G5" t="s">
         <v>597</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="G5" t="s">
-        <v>588</v>
-      </c>
       <c r="H5" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -5769,22 +5802,22 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="G6" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="H6" t="s">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -5796,21 +5829,21 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="G7" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="H7" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -5822,19 +5855,19 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="G8" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="H8" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
@@ -5915,22 +5948,22 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="G2" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H2" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -5944,22 +5977,22 @@
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="G3" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H3" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -5973,22 +6006,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="G4" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H4" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="I4" t="s">
         <v>17</v>
@@ -6002,22 +6035,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="G5" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H5" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -6031,22 +6064,22 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="G6" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H6" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -6060,22 +6093,22 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>623</v>
-      </c>
       <c r="G7" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H7" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -6089,22 +6122,22 @@
         <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="G8" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H8" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
@@ -6118,22 +6151,22 @@
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="G9" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H9" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="I9" t="s">
         <v>17</v>
@@ -6147,22 +6180,22 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="G10" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H10" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -6176,22 +6209,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>637</v>
-      </c>
       <c r="G11" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H11" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -6205,22 +6238,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="G12" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H12" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="I12" t="s">
         <v>17</v>
@@ -6232,7 +6265,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -6241,10 +6274,10 @@
         <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H13" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="I13" t="s">
         <v>17</v>
@@ -6332,22 +6365,22 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="F2" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="G2" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -6361,22 +6394,22 @@
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="F3" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="G3" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -6390,22 +6423,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="F4" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="G4" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -6417,22 +6450,22 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="F5" t="s">
         <v>666</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="F5" t="s">
-        <v>657</v>
-      </c>
       <c r="G5" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -6446,22 +6479,22 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="F6" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="G6" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -6475,22 +6508,22 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="F7" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="G7" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -6502,22 +6535,22 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="F8" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="G8" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -6529,22 +6562,22 @@
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>684</v>
+        <v>693</v>
       </c>
       <c r="F9" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="G9" t="s">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -6614,7 +6647,7 @@
         <v>361</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -6634,24 +6667,24 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I2" t="s">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -6665,26 +6698,26 @@
         <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="5" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I3" t="s">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
@@ -6698,24 +6731,24 @@
         <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5" t="s">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I4" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -6729,24 +6762,24 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I5" t="s">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -6760,24 +6793,24 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>706</v>
+        <v>715</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="5" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I6" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
@@ -6791,24 +6824,24 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I7" t="s">
-        <v>712</v>
+        <v>721</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -6822,24 +6855,24 @@
         <v>39</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I8" t="s">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -6853,24 +6886,24 @@
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="s">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I9" t="s">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -6884,26 +6917,26 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="G10" s="5">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I10" t="s">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
@@ -6917,24 +6950,24 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="5" t="s">
-        <v>726</v>
+        <v>735</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I11" t="s">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -6948,24 +6981,24 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I12" t="s">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
@@ -6979,24 +7012,24 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I13" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -7010,24 +7043,24 @@
         <v>10</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="s">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I14" t="s">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -7041,24 +7074,24 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>741</v>
+        <v>750</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="5" t="s">
-        <v>743</v>
+        <v>752</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I15" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
@@ -7072,24 +7105,24 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="5" t="s">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I16" t="s">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
@@ -7103,24 +7136,24 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="5" t="s">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I17" t="s">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="J17" t="s">
         <v>17</v>
@@ -7134,24 +7167,24 @@
         <v>10</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="5" t="s">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I18" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="J18" t="s">
         <v>17</v>
@@ -7165,24 +7198,24 @@
         <v>10</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I19" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="J19" t="s">
         <v>17</v>
@@ -7196,24 +7229,24 @@
         <v>10</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I20" t="s">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
@@ -7227,24 +7260,24 @@
         <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I21" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="J21" t="s">
         <v>17</v>
@@ -7258,26 +7291,26 @@
         <v>39</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="s">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="G22" s="5">
         <v>4</v>
       </c>
       <c r="H22" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I22" t="s">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="J22" t="s">
         <v>17</v>
@@ -7291,24 +7324,24 @@
         <v>10</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>772</v>
+        <v>781</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="5" t="s">
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I23" t="s">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
@@ -7322,26 +7355,26 @@
         <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="5" t="s">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="G24" s="5">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="I24" t="s">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="J24" t="s">
         <v>17</v>
@@ -7821,7 +7854,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -7830,7 +7863,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -7842,7 +7875,7 @@
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>782</v>
+        <v>791</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -7851,7 +7884,7 @@
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -7863,7 +7896,7 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -7872,7 +7905,7 @@
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>785</v>
+        <v>794</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -7884,7 +7917,7 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>786</v>
+        <v>795</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -7893,7 +7926,7 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -7905,7 +7938,7 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -7914,7 +7947,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>789</v>
+        <v>798</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -7976,7 +8009,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -7985,7 +8018,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>791</v>
+        <v>800</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -8006,7 +8039,7 @@
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>792</v>
+        <v>801</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -8018,7 +8051,7 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -8027,7 +8060,7 @@
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -8039,7 +8072,7 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -8048,7 +8081,7 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -8060,7 +8093,7 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -8069,7 +8102,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>796</v>
+        <v>805</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -8103,16 +8136,16 @@
         <v>6</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>798</v>
+        <v>807</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>799</v>
+        <v>808</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>800</v>
+        <v>809</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -8120,16 +8153,16 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>801</v>
+        <v>810</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>803</v>
+        <v>812</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>804</v>
+        <v>813</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -8137,16 +8170,16 @@
         <v>52</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>806</v>
+        <v>815</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>807</v>
+        <v>816</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8154,16 +8187,16 @@
         <v>89</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>812</v>
+        <v>821</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -8171,14 +8204,14 @@
         <v>171</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -8186,14 +8219,14 @@
         <v>190</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>816</v>
+        <v>825</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8201,14 +8234,14 @@
         <v>259</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
-        <v>819</v>
+        <v>828</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -8216,16 +8249,16 @@
         <v>91</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>820</v>
+        <v>829</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>823</v>
+        <v>832</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -8233,14 +8266,14 @@
         <v>369</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>824</v>
+        <v>833</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>825</v>
+        <v>834</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -8248,14 +8281,14 @@
         <v>516</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>826</v>
+        <v>835</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>827</v>
+        <v>836</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>828</v>
+        <v>837</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -8263,91 +8296,91 @@
         <v>545</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>829</v>
+        <v>838</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>830</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>833</v>
+        <v>842</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>835</v>
+        <v>844</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>836</v>
+        <v>845</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>837</v>
+        <v>846</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="3" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>838</v>
+        <v>847</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="B16" t="s">
-        <v>840</v>
+        <v>849</v>
       </c>
       <c r="C16" t="s">
-        <v>841</v>
+        <v>850</v>
       </c>
       <c r="D16" t="s">
-        <v>842</v>
+        <v>851</v>
       </c>
       <c r="E16" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -8355,16 +8388,16 @@
         <v>565</v>
       </c>
       <c r="B17" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="C17" t="s">
-        <v>845</v>
+        <v>854</v>
       </c>
       <c r="D17" t="s">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="E17" t="s">
-        <v>847</v>
+        <v>856</v>
       </c>
     </row>
   </sheetData>
@@ -8377,7 +8410,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="130" customWidth="1"/>
@@ -8385,92 +8418,92 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>848</v>
+        <v>857</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>855</v>
+        <v>864</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>856</v>
+        <v>865</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>857</v>
+        <v>866</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>858</v>
+        <v>867</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>861</v>
+        <v>870</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>862</v>
+        <v>871</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>864</v>
+        <v>873</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>865</v>
+        <v>874</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -8478,157 +8511,167 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>868</v>
+        <v>877</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>869</v>
+        <v>878</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>872</v>
+        <v>881</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>875</v>
+        <v>884</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>876</v>
+        <v>885</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>878</v>
+        <v>887</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>880</v>
+        <v>889</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>882</v>
+        <v>891</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>883</v>
+        <v>892</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>884</v>
+        <v>893</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>886</v>
+        <v>895</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>892</v>
+        <v>901</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>893</v>
+        <v>902</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>896</v>
+        <v>905</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>907</v>
       </c>
     </row>
   </sheetData>
@@ -8675,22 +8718,22 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="C2" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="D2" t="s">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="E2" t="s">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="F2" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="G2" t="s">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -8704,22 +8747,22 @@
         <v>2027</v>
       </c>
       <c r="B3" t="s">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="C3" t="s">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="D3" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="E3" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="F3" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="G3" t="s">
-        <v>906</v>
+        <v>917</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -8733,22 +8776,22 @@
         <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="C4" t="s">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="D4" t="s">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="E4" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="F4" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="G4" t="s">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -8762,22 +8805,22 @@
         <v>2027</v>
       </c>
       <c r="B5" t="s">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="C5" t="s">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="D5" t="s">
-        <v>911</v>
+        <v>922</v>
       </c>
       <c r="E5" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="F5" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="G5" t="s">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -8788,7 +8831,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 

--- a/data/2026_VBS_Boat_Inventory_Master.xlsx
+++ b/data/2026_VBS_Boat_Inventory_Master.xlsx
@@ -2139,7 +2139,7 @@
     <t>N83139</t>
   </si>
   <si>
-    <t>Stone Harbor Marina</t>
+    <t>Stone Harbor Yacht Sales &amp; Marina</t>
   </si>
   <si>
     <t>stone-harbor-marina__cobia__265-cc__2026</t>

--- a/data/2026_VBS_Boat_Inventory_Master.xlsx
+++ b/data/2026_VBS_Boat_Inventory_Master.xlsx
@@ -27,7 +27,7 @@
     <sheet sheetId="18" name="South Jersey" state="visible" r:id="rId21"/>
     <sheet sheetId="19" name="Stone Harbor" state="visible" r:id="rId22"/>
     <sheet sheetId="20" name="TBD - Alara Donzi Fairline" state="visible" r:id="rId23"/>
-    <sheet sheetId="21" name="TBD - Contender Monterey" state="visible" r:id="rId24"/>
+    <sheet sheetId="21" name="Valhalla" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Dealer Contacts" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="Notes" state="visible" r:id="rId26"/>
     <sheet sheetId="24" name="Irwin" state="visible" r:id="rId27"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="948">
   <si>
     <t>YEAR</t>
   </si>
@@ -2436,25 +2436,85 @@
     <t>tbd-alara-donzi-fairline__twin-vee-boats</t>
   </si>
   <si>
-    <t>Contender Boats</t>
-  </si>
-  <si>
-    <t>tbd-contender-monterey__contender-boats</t>
-  </si>
-  <si>
-    <t>tbd-contender-monterey__monterey-boats</t>
-  </si>
-  <si>
-    <t>tbd-contender-monterey__regal-boats</t>
-  </si>
-  <si>
-    <t>Sportsman Boats</t>
-  </si>
-  <si>
-    <t>tbd-contender-monterey__sportsman-boats</t>
-  </si>
-  <si>
-    <t>tbd-contender-monterey__valhalla-boats</t>
+    <t>Monterey</t>
+  </si>
+  <si>
+    <t>Elite 27 OB</t>
+  </si>
+  <si>
+    <t>https://www.valhallayachtsales.com/NEW-Inventory-2027-Monterey-Boat-ELITE-27-OB-New-Gretna-NJ-18961130?ref=list</t>
+  </si>
+  <si>
+    <t>Valhalla Yacht Sales</t>
+  </si>
+  <si>
+    <t>valhalla-yacht-sales__monterey__elite-27-ob__2027</t>
+  </si>
+  <si>
+    <t>unit listing (Ed Szambelak email, Sep 1)</t>
+  </si>
+  <si>
+    <t>Contender</t>
+  </si>
+  <si>
+    <t>39ST</t>
+  </si>
+  <si>
+    <t>https://www.valhallayachtsales.com/NEW-Inventory-2026-Contender-Boat-39ST-New-Gretna-NJ-18107720?ref=list</t>
+  </si>
+  <si>
+    <t>https://www.contenderboats.com/</t>
+  </si>
+  <si>
+    <t>valhalla-yacht-sales__contender__39st__2026</t>
+  </si>
+  <si>
+    <t>Sportsman</t>
+  </si>
+  <si>
+    <t>Open 302</t>
+  </si>
+  <si>
+    <t>https://www.valhallayachtsales.com/NEW-Inventory-2026-Sportsman-Boat-Open-302-Center-Console-New-Gretna-NJ-18807462?ref=list</t>
+  </si>
+  <si>
+    <t>https://www.sportsmanboatsmfg.com/</t>
+  </si>
+  <si>
+    <t>valhalla-yacht-sales__sportsman__open-302__2026</t>
+  </si>
+  <si>
+    <t>Valhalla</t>
+  </si>
+  <si>
+    <t>V-41</t>
+  </si>
+  <si>
+    <t>https://www.valhallayachtsales.com/NEW-Inventory-2027-Valhalla-Boat-V-41-Wrightsville-Beach-18961125?ref=list</t>
+  </si>
+  <si>
+    <t>https://www.valhallaboatworks.com/</t>
+  </si>
+  <si>
+    <t>valhalla-yacht-sales__valhalla__v-41__2027</t>
+  </si>
+  <si>
+    <t>unit listing, stock photos only per Ed (Sep 1)</t>
+  </si>
+  <si>
+    <t>Phenom</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>https://www.valhallayachtsales.com/NEW-Inventory-2027-Phenom-Boat-43-Center-Console-Riviera-Beach-FL-18976953?ref=list</t>
+  </si>
+  <si>
+    <t>https://www.phenomyachts.com/</t>
+  </si>
+  <si>
+    <t>valhalla-yacht-sales__phenom__43__2027</t>
   </si>
   <si>
     <t>CONTACT NAME(S)</t>
@@ -2608,6 +2668,18 @@
   </si>
   <si>
     <t>Christian Matthews email, Sep 1 (forwarded by Giselle)</t>
+  </si>
+  <si>
+    <t>Ed Szambelak, Sales Coordinator, Valhalla Yacht Sales North (eszambelak@valhallaboatsales.com, office (609) 296-2388 ext. 1116, cell (267) 730-2081)</t>
+  </si>
+  <si>
+    <t>eszambelak@valhallaboatsales.com</t>
+  </si>
+  <si>
+    <t>(267) 730-2081</t>
+  </si>
+  <si>
+    <t>Ed Szambelak email, Sep 1 (forwarded by Giselle Sep 5)</t>
   </si>
   <si>
     <t>2026 AC In-Water Virtual Boat Show - Boat Inventory Master (built Aug 30, 2026)</t>
@@ -8007,108 +8079,148 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2">
+        <v>2027</v>
+      </c>
+      <c r="B2" t="s">
         <v>799</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="C2" t="s">
+        <v>800</v>
+      </c>
+      <c r="D2" t="s">
+        <v>801</v>
+      </c>
+      <c r="E2" t="s">
+        <v>182</v>
+      </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>802</v>
       </c>
       <c r="G2" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>173</v>
+        <v>804</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C3" t="s">
+        <v>806</v>
+      </c>
+      <c r="D3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E3" t="s">
+        <v>808</v>
+      </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>802</v>
       </c>
       <c r="G3" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>173</v>
+        <v>804</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4" t="s">
+        <v>810</v>
+      </c>
+      <c r="C4" t="s">
+        <v>811</v>
+      </c>
+      <c r="D4" t="s">
+        <v>812</v>
+      </c>
+      <c r="E4" t="s">
+        <v>813</v>
+      </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>802</v>
       </c>
       <c r="G4" t="s">
+        <v>814</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2027</v>
+      </c>
+      <c r="B5" t="s">
+        <v>815</v>
+      </c>
+      <c r="C5" t="s">
+        <v>816</v>
+      </c>
+      <c r="D5" t="s">
+        <v>817</v>
+      </c>
+      <c r="E5" t="s">
+        <v>818</v>
+      </c>
+      <c r="F5" t="s">
         <v>802</v>
       </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
       <c r="G5" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>173</v>
+        <v>820</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="A6">
+        <v>2027</v>
+      </c>
+      <c r="B6" t="s">
+        <v>821</v>
+      </c>
+      <c r="C6" t="s">
+        <v>822</v>
+      </c>
+      <c r="D6" t="s">
+        <v>823</v>
+      </c>
+      <c r="E6" t="s">
+        <v>824</v>
+      </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>802</v>
       </c>
       <c r="G6" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>173</v>
+        <v>820</v>
       </c>
     </row>
   </sheetData>
@@ -8121,7 +8233,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -8136,16 +8248,16 @@
         <v>6</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>806</v>
+        <v>826</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>807</v>
+        <v>827</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>808</v>
+        <v>828</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>809</v>
+        <v>829</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -8153,16 +8265,16 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>813</v>
+        <v>833</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -8170,16 +8282,16 @@
         <v>52</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>814</v>
+        <v>834</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>816</v>
+        <v>836</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>817</v>
+        <v>837</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8187,16 +8299,16 @@
         <v>89</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>818</v>
+        <v>838</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>819</v>
+        <v>839</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>820</v>
+        <v>840</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>821</v>
+        <v>841</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -8204,14 +8316,14 @@
         <v>171</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>822</v>
+        <v>842</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>824</v>
+        <v>844</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -8219,14 +8331,14 @@
         <v>190</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>826</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8234,14 +8346,14 @@
         <v>259</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
-        <v>828</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -8249,16 +8361,16 @@
         <v>91</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>831</v>
+        <v>851</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>832</v>
+        <v>852</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -8266,14 +8378,14 @@
         <v>369</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>833</v>
+        <v>853</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>834</v>
+        <v>854</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -8281,14 +8393,14 @@
         <v>516</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>835</v>
+        <v>855</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>836</v>
+        <v>856</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -8296,14 +8408,14 @@
         <v>545</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -8311,14 +8423,14 @@
         <v>597</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>841</v>
+        <v>861</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -8326,16 +8438,16 @@
         <v>624</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>843</v>
+        <v>863</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>844</v>
+        <v>864</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>845</v>
+        <v>865</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -8343,14 +8455,14 @@
         <v>666</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>846</v>
+        <v>866</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>826</v>
+        <v>846</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -8359,28 +8471,28 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="3" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>847</v>
+        <v>867</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B16" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="C16" t="s">
-        <v>850</v>
+        <v>870</v>
       </c>
       <c r="D16" t="s">
-        <v>851</v>
+        <v>871</v>
       </c>
       <c r="E16" t="s">
-        <v>852</v>
+        <v>872</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -8388,16 +8500,33 @@
         <v>565</v>
       </c>
       <c r="B17" t="s">
-        <v>853</v>
+        <v>873</v>
       </c>
       <c r="C17" t="s">
-        <v>854</v>
+        <v>874</v>
       </c>
       <c r="D17" t="s">
-        <v>855</v>
+        <v>875</v>
       </c>
       <c r="E17" t="s">
-        <v>856</v>
+        <v>876</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>802</v>
+      </c>
+      <c r="B18" t="s">
+        <v>877</v>
+      </c>
+      <c r="C18" t="s">
+        <v>878</v>
+      </c>
+      <c r="D18" t="s">
+        <v>879</v>
+      </c>
+      <c r="E18" t="s">
+        <v>880</v>
       </c>
     </row>
   </sheetData>
@@ -8418,92 +8547,92 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>857</v>
+        <v>881</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>858</v>
+        <v>882</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>859</v>
+        <v>883</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>860</v>
+        <v>884</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>861</v>
+        <v>885</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>862</v>
+        <v>886</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>863</v>
+        <v>887</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>864</v>
+        <v>888</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>865</v>
+        <v>889</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>866</v>
+        <v>890</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>867</v>
+        <v>891</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>868</v>
+        <v>892</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>869</v>
+        <v>893</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>870</v>
+        <v>894</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>871</v>
+        <v>895</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>872</v>
+        <v>896</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>873</v>
+        <v>897</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>874</v>
+        <v>898</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -8511,167 +8640,167 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>875</v>
+        <v>899</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>876</v>
+        <v>900</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>877</v>
+        <v>901</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>878</v>
+        <v>902</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>879</v>
+        <v>903</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>880</v>
+        <v>904</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>881</v>
+        <v>905</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>883</v>
+        <v>907</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>884</v>
+        <v>908</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>885</v>
+        <v>909</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>886</v>
+        <v>910</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>887</v>
+        <v>911</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>888</v>
+        <v>912</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>889</v>
+        <v>913</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>890</v>
+        <v>914</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>891</v>
+        <v>915</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>892</v>
+        <v>916</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>893</v>
+        <v>917</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>894</v>
+        <v>918</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>895</v>
+        <v>919</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>896</v>
+        <v>920</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>897</v>
+        <v>921</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>898</v>
+        <v>922</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>899</v>
+        <v>923</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>900</v>
+        <v>924</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>901</v>
+        <v>925</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>902</v>
+        <v>926</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>903</v>
+        <v>927</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>904</v>
+        <v>928</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>905</v>
+        <v>929</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>906</v>
+        <v>930</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>907</v>
+        <v>931</v>
       </c>
     </row>
   </sheetData>
@@ -8718,22 +8847,22 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="C2" t="s">
-        <v>909</v>
+        <v>933</v>
       </c>
       <c r="D2" t="s">
-        <v>910</v>
+        <v>934</v>
       </c>
       <c r="E2" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="F2" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="G2" t="s">
-        <v>912</v>
+        <v>936</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -8747,22 +8876,22 @@
         <v>2027</v>
       </c>
       <c r="B3" t="s">
-        <v>913</v>
+        <v>937</v>
       </c>
       <c r="C3" t="s">
-        <v>914</v>
+        <v>938</v>
       </c>
       <c r="D3" t="s">
-        <v>915</v>
+        <v>939</v>
       </c>
       <c r="E3" t="s">
-        <v>916</v>
+        <v>940</v>
       </c>
       <c r="F3" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="G3" t="s">
-        <v>917</v>
+        <v>941</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -8776,22 +8905,22 @@
         <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>913</v>
+        <v>937</v>
       </c>
       <c r="C4" t="s">
-        <v>918</v>
+        <v>942</v>
       </c>
       <c r="D4" t="s">
-        <v>919</v>
+        <v>943</v>
       </c>
       <c r="E4" t="s">
-        <v>916</v>
+        <v>940</v>
       </c>
       <c r="F4" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="G4" t="s">
-        <v>920</v>
+        <v>944</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -8805,22 +8934,22 @@
         <v>2027</v>
       </c>
       <c r="B5" t="s">
-        <v>913</v>
+        <v>937</v>
       </c>
       <c r="C5" t="s">
-        <v>921</v>
+        <v>945</v>
       </c>
       <c r="D5" t="s">
-        <v>922</v>
+        <v>946</v>
       </c>
       <c r="E5" t="s">
-        <v>916</v>
+        <v>940</v>
       </c>
       <c r="F5" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="G5" t="s">
-        <v>923</v>
+        <v>947</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>

--- a/data/2026_VBS_Boat_Inventory_Master.xlsx
+++ b/data/2026_VBS_Boat_Inventory_Master.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2240" uniqueCount="954">
   <si>
     <t>YEAR</t>
   </si>
@@ -849,6 +849,18 @@
     <t>formula-boats__formula-boats__310-br</t>
   </si>
   <si>
+    <t>500 SSC</t>
+  </si>
+  <si>
+    <t>https://www.formulaboats.com/boats/500-super-sport-crossover/</t>
+  </si>
+  <si>
+    <t>formula-boats__formula-boats__500-ssc__2026</t>
+  </si>
+  <si>
+    <t>manufacturer model page (Tonya Hamilton email, Sep 8)</t>
+  </si>
+  <si>
     <t>Ranger Tugs Boats</t>
   </si>
   <si>
@@ -2580,10 +2592,16 @@
     <t>PLAN B fallback (decided Aug 30) - replace when the dealer supplies a lead inbox. Not yet supplied (emailed Aug 22, no reply)</t>
   </si>
   <si>
-    <t>Tonya Hamilton (ext 1118), Steve Anthony (formulasteve1@gmail.com), Scott Smith (scotts@formulaboats.com) - none designated for leads yet</t>
-  </si>
-  <si>
-    <t>PLAN B fallback (decided Aug 30) - replace when the dealer supplies a lead inbox. Not yet supplied - contacts on file: Tonya Hamilton tlhamilton@formulaboats.com ext 1118, Steve Anthony formulasteve1@gmail.com, Scott Smith scotts@formulaboats.com</t>
+    <t>Maverick Shifferly (mavericks@formulaboats.com, cell 260-223-4710); Tonya Hamilton 260-724-1118 ext 1118</t>
+  </si>
+  <si>
+    <t>mavericks@formulaboats.com</t>
+  </si>
+  <si>
+    <t>260-223-4710</t>
+  </si>
+  <si>
+    <t>Tonya Hamilton email, Sep 8, 2026</t>
   </si>
   <si>
     <t>Richard Johanson - BDC per Greta Andrews (Regional Events and Marketing); one line covers ALL MarineMax locations for this show; supplied by Kate Hogan and Greta</t>
@@ -3583,10 +3601,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -3606,28 +3624,28 @@
         <v>2026</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -3641,28 +3659,28 @@
         <v>2026</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="H3" t="s">
         <v>373</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="H3" t="s">
-        <v>369</v>
-      </c>
       <c r="I3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
@@ -3676,28 +3694,28 @@
         <v>2026</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H4" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I4" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -3711,28 +3729,28 @@
         <v>2026</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="H5" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I5" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -3746,28 +3764,28 @@
         <v>2026</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="H6" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I6" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
@@ -3781,28 +3799,28 @@
         <v>2026</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="H7" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I7" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -3816,28 +3834,28 @@
         <v>2026</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H8" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I8" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -3851,28 +3869,28 @@
         <v>2026</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="H9" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I9" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -3886,28 +3904,28 @@
         <v>2026</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="H10" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I10" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
@@ -3921,28 +3939,28 @@
         <v>2026</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="H11" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I11" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -3956,28 +3974,28 @@
         <v>2026</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>410</v>
-      </c>
       <c r="F12" s="5" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H12" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I12" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
@@ -3991,28 +4009,28 @@
         <v>2026</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H13" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I13" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -4026,28 +4044,28 @@
         <v>2026</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="H14" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I14" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -4061,28 +4079,28 @@
         <v>2026</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="H15" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I15" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
@@ -4096,28 +4114,28 @@
         <v>2025</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="H16" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
@@ -4131,28 +4149,28 @@
         <v>2026</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H17" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I17" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="J17" t="s">
         <v>17</v>
@@ -4166,28 +4184,28 @@
         <v>2026</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H18" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I18" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="J18" t="s">
         <v>17</v>
@@ -4201,28 +4219,28 @@
         <v>2026</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>444</v>
-      </c>
       <c r="F19" s="5" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="H19" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I19" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="J19" t="s">
         <v>17</v>
@@ -4236,28 +4254,28 @@
         <v>2025</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>449</v>
-      </c>
       <c r="E20" s="6" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="H20" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I20" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
@@ -4271,28 +4289,28 @@
         <v>2026</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="H21" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I21" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="J21" t="s">
         <v>17</v>
@@ -4306,28 +4324,28 @@
         <v>2026</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="H22" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I22" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="J22" t="s">
         <v>17</v>
@@ -4341,28 +4359,28 @@
         <v>2026</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="H23" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I23" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
@@ -4376,28 +4394,28 @@
         <v>2026</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="H24" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I24" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="J24" t="s">
         <v>17</v>
@@ -4411,28 +4429,28 @@
         <v>2025</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="H25" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I25" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="J25" t="s">
         <v>17</v>
@@ -4446,28 +4464,28 @@
         <v>2025</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>478</v>
-      </c>
       <c r="F26" s="5" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="H26" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I26" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
@@ -4481,28 +4499,28 @@
         <v>2026</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="H27" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I27" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J27" t="s">
         <v>17</v>
@@ -4516,28 +4534,28 @@
         <v>2025</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="H28" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I28" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
@@ -4551,28 +4569,28 @@
         <v>2025</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H29" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I29" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
@@ -4586,28 +4604,28 @@
         <v>2025</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H30" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I30" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="J30" t="s">
         <v>17</v>
@@ -4619,26 +4637,26 @@
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H31" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I31" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="J31" t="s">
         <v>17</v>
@@ -4650,26 +4668,26 @@
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H32" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I32" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J32" t="s">
         <v>17</v>
@@ -4797,22 +4815,22 @@
         <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -4826,22 +4844,22 @@
         <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>515</v>
-      </c>
       <c r="F3" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G3" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -4855,22 +4873,22 @@
         <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G4" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -4884,22 +4902,22 @@
         <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F5" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G5" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -4913,22 +4931,22 @@
         <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F6" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G6" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -4940,22 +4958,22 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F7" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G7" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -4967,22 +4985,22 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F8" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G8" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -5060,7 +5078,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -5069,7 +5087,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -5131,7 +5149,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -5140,7 +5158,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -5152,7 +5170,7 @@
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -5161,7 +5179,7 @@
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -5225,22 +5243,22 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="F2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -5254,22 +5272,22 @@
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>544</v>
-      </c>
       <c r="F3" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G3" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -5283,22 +5301,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G4" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -5312,22 +5330,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F5" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G5" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -5399,7 +5417,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -5408,7 +5426,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -5420,7 +5438,7 @@
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -5429,7 +5447,7 @@
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -5443,22 +5461,22 @@
         <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C4" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D4" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="E4" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F4" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -5472,22 +5490,22 @@
         <v>2026</v>
       </c>
       <c r="B5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C5" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D5" t="s">
+        <v>572</v>
+      </c>
+      <c r="E5" t="s">
         <v>568</v>
       </c>
-      <c r="E5" t="s">
-        <v>564</v>
-      </c>
       <c r="F5" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G5" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -5501,22 +5519,22 @@
         <v>2026</v>
       </c>
       <c r="B6" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C6" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D6" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E6" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F6" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G6" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -5530,22 +5548,22 @@
         <v>2026</v>
       </c>
       <c r="B7" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C7" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D7" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E7" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F7" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G7" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -5559,22 +5577,22 @@
         <v>2027</v>
       </c>
       <c r="B8" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C8" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D8" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="E8" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="F8" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G8" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -5588,22 +5606,22 @@
         <v>2027</v>
       </c>
       <c r="B9" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C9" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D9" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="E9" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="F9" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G9" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -5617,22 +5635,22 @@
         <v>2027</v>
       </c>
       <c r="B10" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C10" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="D10" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E10" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="F10" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G10" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
@@ -5646,22 +5664,22 @@
         <v>2027</v>
       </c>
       <c r="B11" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C11" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="D11" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="E11" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="F11" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G11" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -5675,22 +5693,22 @@
         <v>2027</v>
       </c>
       <c r="B12" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C12" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D12" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="E12" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="F12" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G12" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
@@ -5755,25 +5773,25 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="G2" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="H2" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -5787,22 +5805,22 @@
         <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>596</v>
-      </c>
       <c r="G3" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="H3" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -5816,22 +5834,22 @@
         <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="G4" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="H4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="I4" t="s">
         <v>17</v>
@@ -5845,22 +5863,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="G5" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="H5" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -5874,22 +5892,22 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="G6" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="H6" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -5901,21 +5919,21 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="G7" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="H7" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -5927,19 +5945,19 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="G8" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="H8" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
@@ -6020,22 +6038,22 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="G2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H2" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -6049,22 +6067,22 @@
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>623</v>
-      </c>
       <c r="G3" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H3" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -6078,22 +6096,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="G4" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H4" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="I4" t="s">
         <v>17</v>
@@ -6107,22 +6125,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="G5" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H5" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -6136,22 +6154,22 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="G6" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H6" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -6165,22 +6183,22 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="G7" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H7" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -6194,22 +6212,22 @@
         <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G8" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H8" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
@@ -6223,22 +6241,22 @@
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G9" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H9" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="I9" t="s">
         <v>17</v>
@@ -6252,22 +6270,22 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G10" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H10" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -6281,22 +6299,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G11" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H11" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -6310,22 +6328,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G12" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H12" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="I12" t="s">
         <v>17</v>
@@ -6337,7 +6355,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -6346,10 +6364,10 @@
         <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H13" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="I13" t="s">
         <v>17</v>
@@ -6437,22 +6455,22 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="F2" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G2" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -6466,22 +6484,22 @@
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>665</v>
-      </c>
       <c r="F3" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G3" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -6495,22 +6513,22 @@
         <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="F4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G4" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -6522,22 +6540,22 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="F5" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G5" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -6551,22 +6569,22 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="F6" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G6" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -6580,22 +6598,22 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="F7" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G7" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -6607,22 +6625,22 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="F8" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G8" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -6634,22 +6652,22 @@
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="F9" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G9" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -6716,10 +6734,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -6739,24 +6757,24 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I2" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -6770,26 +6788,26 @@
         <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="5" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I3" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
@@ -6803,24 +6821,24 @@
         <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I4" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -6834,24 +6852,24 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I5" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -6865,24 +6883,24 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="5" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I6" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
@@ -6896,24 +6914,24 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I7" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -6927,24 +6945,24 @@
         <v>39</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="5" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I8" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -6958,24 +6976,24 @@
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I9" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -6989,26 +7007,26 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="G10" s="5">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I10" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
@@ -7022,24 +7040,24 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="5" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I11" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -7053,24 +7071,24 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I12" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
@@ -7084,24 +7102,24 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I13" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -7115,24 +7133,24 @@
         <v>10</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I14" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -7146,24 +7164,24 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="5" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I15" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
@@ -7177,24 +7195,24 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I16" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
@@ -7208,24 +7226,24 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="5" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I17" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="J17" t="s">
         <v>17</v>
@@ -7239,24 +7257,24 @@
         <v>10</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="5" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I18" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="J18" t="s">
         <v>17</v>
@@ -7270,24 +7288,24 @@
         <v>10</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="5" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I19" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="J19" t="s">
         <v>17</v>
@@ -7301,24 +7319,24 @@
         <v>10</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I20" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
@@ -7332,24 +7350,24 @@
         <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I21" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="J21" t="s">
         <v>17</v>
@@ -7363,26 +7381,26 @@
         <v>39</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="5" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="G22" s="5">
         <v>4</v>
       </c>
       <c r="H22" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I22" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="J22" t="s">
         <v>17</v>
@@ -7396,24 +7414,24 @@
         <v>10</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I23" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
@@ -7427,26 +7445,26 @@
         <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="5" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="G24" s="5">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I24" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="J24" t="s">
         <v>17</v>
@@ -7926,7 +7944,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -7935,7 +7953,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -7947,7 +7965,7 @@
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -7956,7 +7974,7 @@
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -7968,7 +7986,7 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -7977,7 +7995,7 @@
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -7989,7 +8007,7 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -7998,7 +8016,7 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -8010,7 +8028,7 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -8019,7 +8037,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -8083,28 +8101,28 @@
         <v>2027</v>
       </c>
       <c r="B2" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C2" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="D2" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="E2" t="s">
         <v>182</v>
       </c>
       <c r="F2" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="G2" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -8112,28 +8130,28 @@
         <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C3" t="s">
+        <v>810</v>
+      </c>
+      <c r="D3" t="s">
+        <v>811</v>
+      </c>
+      <c r="E3" t="s">
+        <v>812</v>
+      </c>
+      <c r="F3" t="s">
         <v>806</v>
       </c>
-      <c r="D3" t="s">
-        <v>807</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>813</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
         <v>808</v>
-      </c>
-      <c r="F3" t="s">
-        <v>802</v>
-      </c>
-      <c r="G3" t="s">
-        <v>809</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -8141,28 +8159,28 @@
         <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C4" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D4" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="E4" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="F4" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="G4" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -8170,28 +8188,28 @@
         <v>2027</v>
       </c>
       <c r="B5" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C5" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D5" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="E5" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="F5" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="G5" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -8199,28 +8217,28 @@
         <v>2027</v>
       </c>
       <c r="B6" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C6" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D6" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="E6" t="s">
+        <v>828</v>
+      </c>
+      <c r="F6" t="s">
+        <v>806</v>
+      </c>
+      <c r="G6" t="s">
+        <v>829</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
         <v>824</v>
-      </c>
-      <c r="F6" t="s">
-        <v>802</v>
-      </c>
-      <c r="G6" t="s">
-        <v>825</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" t="s">
-        <v>820</v>
       </c>
     </row>
   </sheetData>
@@ -8248,16 +8266,16 @@
         <v>6</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -8265,16 +8283,16 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -8282,16 +8300,16 @@
         <v>52</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8299,16 +8317,16 @@
         <v>89</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -8316,14 +8334,14 @@
         <v>171</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -8331,14 +8349,14 @@
         <v>190</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8346,14 +8364,16 @@
         <v>259</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>843</v>
-      </c>
-      <c r="D7" s="3"/>
+        <v>852</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>853</v>
+      </c>
       <c r="E7" s="3" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -8361,172 +8381,172 @@
         <v>91</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="3" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="B16" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="C16" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="D16" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="E16" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B17" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="C17" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="D17" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="E17" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B18" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="C18" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="D18" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="E18" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
     </row>
   </sheetData>
@@ -8547,92 +8567,92 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -8640,167 +8660,167 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
     </row>
   </sheetData>
@@ -8847,22 +8867,22 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="C2" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="D2" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="E2" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="F2" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="G2" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -8876,22 +8896,22 @@
         <v>2027</v>
       </c>
       <c r="B3" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="C3" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="D3" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="E3" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="F3" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="G3" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -8905,22 +8925,22 @@
         <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="C4" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="D4" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="E4" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="F4" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="G4" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -8934,22 +8954,22 @@
         <v>2027</v>
       </c>
       <c r="B5" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="C5" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="D5" t="s">
+        <v>952</v>
+      </c>
+      <c r="E5" t="s">
         <v>946</v>
       </c>
-      <c r="E5" t="s">
-        <v>940</v>
-      </c>
       <c r="F5" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="G5" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -10471,7 +10491,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -10590,6 +10610,35 @@
       </c>
       <c r="I4" t="s">
         <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2026</v>
+      </c>
+      <c r="B5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E5" t="s">
+        <v>262</v>
+      </c>
+      <c r="F5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G5" t="s">
+        <v>272</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -10653,7 +10702,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -10662,7 +10711,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -10724,7 +10773,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -10733,7 +10782,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -10801,22 +10850,22 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G2" t="s">
         <v>91</v>
       </c>
       <c r="H2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -10830,22 +10879,22 @@
         <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G3" t="s">
         <v>91</v>
       </c>
       <c r="H3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -10859,22 +10908,22 @@
         <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G4" t="s">
         <v>91</v>
       </c>
       <c r="H4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="I4" t="s">
         <v>17</v>
@@ -10888,22 +10937,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G5" t="s">
         <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -10917,22 +10966,22 @@
         <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G6" t="s">
         <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -10946,22 +10995,22 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G7" t="s">
         <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -10975,22 +11024,22 @@
         <v>39</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G8" t="s">
         <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
@@ -11004,22 +11053,22 @@
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G9" t="s">
         <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="I9" t="s">
         <v>17</v>
@@ -11033,22 +11082,22 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G10" t="s">
         <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -11062,22 +11111,22 @@
         <v>39</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G11" t="s">
         <v>91</v>
       </c>
       <c r="H11" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -11091,22 +11140,22 @@
         <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G12" t="s">
         <v>91</v>
       </c>
       <c r="H12" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I12" t="s">
         <v>17</v>
@@ -11120,22 +11169,22 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G13" t="s">
         <v>91</v>
       </c>
       <c r="H13" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I13" t="s">
         <v>17</v>
@@ -11149,22 +11198,22 @@
         <v>10</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G14" t="s">
         <v>91</v>
       </c>
       <c r="H14" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -11178,22 +11227,22 @@
         <v>39</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G15" t="s">
         <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -11207,22 +11256,22 @@
         <v>39</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G16" t="s">
         <v>91</v>
       </c>
       <c r="H16" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I16" t="s">
         <v>17</v>
@@ -11236,22 +11285,22 @@
         <v>39</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G17" t="s">
         <v>91</v>
       </c>
       <c r="H17" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
@@ -11265,22 +11314,22 @@
         <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G18" t="s">
         <v>91</v>
       </c>
       <c r="H18" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -11300,19 +11349,19 @@
         <v>85</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>87</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G19" t="s">
         <v>91</v>
       </c>
       <c r="H19" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="I19" t="s">
         <v>89</v>
@@ -11336,13 +11385,13 @@
         <v>94</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G20" t="s">
         <v>91</v>
       </c>
       <c r="H20" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I20" t="s">
         <v>89</v>
@@ -11366,13 +11415,13 @@
         <v>98</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G21" t="s">
         <v>91</v>
       </c>
       <c r="H21" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="I21" t="s">
         <v>89</v>
@@ -11396,13 +11445,13 @@
         <v>102</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G22" t="s">
         <v>91</v>
       </c>
       <c r="H22" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="I22" t="s">
         <v>89</v>
@@ -11422,19 +11471,19 @@
         <v>104</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>106</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G23" t="s">
         <v>91</v>
       </c>
       <c r="H23" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I23" t="s">
         <v>89</v>
@@ -11454,19 +11503,19 @@
         <v>108</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>110</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G24" t="s">
         <v>91</v>
       </c>
       <c r="H24" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I24" t="s">
         <v>89</v>
@@ -11481,22 +11530,22 @@
         <v>116</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G25" t="s">
         <v>91</v>
       </c>
       <c r="H25" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="I25" t="s">
         <v>17</v>
@@ -11517,16 +11566,16 @@
         <v>118</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G26" t="s">
         <v>91</v>
       </c>
       <c r="H26" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I26" t="s">
         <v>89</v>
@@ -11546,19 +11595,19 @@
         <v>121</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G27" t="s">
         <v>91</v>
       </c>
       <c r="H27" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="I27" t="s">
         <v>89</v>
@@ -11575,22 +11624,22 @@
         <v>116</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G28" t="s">
         <v>91</v>
       </c>
       <c r="H28" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="I28" t="s">
         <v>17</v>
@@ -11610,19 +11659,19 @@
         <v>125</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>127</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G29" t="s">
         <v>91</v>
       </c>
       <c r="H29" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="I29" t="s">
         <v>89</v>
@@ -11648,13 +11697,13 @@
         <v>131</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G30" t="s">
         <v>91</v>
       </c>
       <c r="H30" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="I30" t="s">
         <v>89</v>
@@ -11675,16 +11724,16 @@
         <v>135</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G31" t="s">
         <v>91</v>
       </c>
       <c r="H31" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="I31" t="s">
         <v>89</v>
